--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_93_R10.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_93_R10.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5148</v>
+        <v>3.5724</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2825</v>
+        <v>4.2393</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7677</v>
+        <v>-0.6669</v>
       </c>
       <c r="G2" t="n">
         <v>-1.2308</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7947</v>
+        <v>0.8522</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0815</v>
+        <v>1.0383</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2869</v>
+        <v>-0.186</v>
       </c>
       <c r="V2" t="n">
         <v>2.7912</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4511</v>
+        <v>2.3408</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3642</v>
+        <v>6.5429</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.913</v>
+        <v>-4.2021</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0832</v>
+        <v>2.1954</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7721</v>
+        <v>0.7166</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3111</v>
+        <v>1.4789</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4478</v>
+        <v>4.4082</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5546</v>
+        <v>1.8219</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8932</v>
+        <v>2.5863</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3646</v>
+        <v>-2.2127</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2175</v>
+        <v>-1.1053</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5821</v>
+        <v>-1.1074</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0444</v>
+        <v>-1.0712</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9164</v>
+        <v>0.1654</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9607</v>
+        <v>-1.2366</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2836</v>
+        <v>2.1444</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>4.2888</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2836</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>J. AYAYI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0776</v>
+        <v>1.274</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4813</v>
+        <v>1.6856</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.4037</v>
+        <v>-0.4116</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1954</v>
+        <v>2.067</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7166</v>
+        <v>1.7826</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4789</v>
+        <v>0.2844</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4082</v>
+        <v>2.5424</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8219</v>
+        <v>2.151</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5863</v>
+        <v>0.3914</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2127</v>
+        <v>-0.4755</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1053</v>
+        <v>-0.3684</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1074</v>
+        <v>-0.107</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.3344</v>
+        <v>0.5111</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8962</v>
+        <v>0.3029</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.4383</v>
+        <v>0.2082</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>4.2888</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. AYAYI</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9798</v>
+        <v>1.2488</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2571</v>
+        <v>2.1283</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2772</v>
+        <v>-0.8794</v>
       </c>
       <c r="G5" t="n">
-        <v>2.067</v>
+        <v>1.0832</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7826</v>
+        <v>0.7721</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2844</v>
+        <v>0.3111</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5424</v>
+        <v>1.4478</v>
       </c>
       <c r="K5" t="n">
-        <v>2.151</v>
+        <v>0.5546</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3914</v>
+        <v>0.8932</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4755</v>
+        <v>-0.3646</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3684</v>
+        <v>0.2175</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.107</v>
+        <v>-0.5821</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>0.217</v>
+        <v>-0.2467</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1256</v>
+        <v>0.6805</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3427</v>
+        <v>-0.9271</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.169</v>
+        <v>0.3956</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3462</v>
+        <v>1.6719</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1772</v>
+        <v>-1.2763</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9122</v>
+        <v>0.2416</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5677</v>
+        <v>-0.6852</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3446</v>
+        <v>0.9268</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3214</v>
+        <v>2.1182</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.5055</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.184</v>
+        <v>2.0342</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5908</v>
+        <v>-1.8766</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0622</v>
+        <v>-0.7692</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5286</v>
+        <v>-1.1074</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1892</v>
+        <v>-0.9878</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9752</v>
+        <v>0.0356</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2139</v>
+        <v>-1.0233</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3943</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.444</v>
+        <v>-0.5545</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0559</v>
+        <v>-1.0991</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6118</v>
+        <v>0.5446</v>
       </c>
       <c r="G7" t="n">
         <v>-3.1418</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2133</v>
+        <v>1.1029</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0815</v>
+        <v>1.0383</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1318</v>
+        <v>0.0646</v>
       </c>
       <c r="V7" t="n">
         <v>0.7886</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5474</v>
+        <v>-1.2628</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9641999999999999</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5116</v>
+        <v>-0.3269</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2416</v>
+        <v>-2.9122</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6852</v>
+        <v>-2.5677</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9268</v>
+        <v>-0.3446</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1182</v>
+        <v>-1.3214</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08400000000000001</v>
+        <v>-1.5055</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0342</v>
+        <v>0.184</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8766</v>
+        <v>-1.5908</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7692</v>
+        <v>-1.0622</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1074</v>
+        <v>-0.5286</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.9307</v>
+        <v>0.0953</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6721</v>
+        <v>0.3855</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2586</v>
+        <v>-0.2902</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.3943</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>E. SHAHRVIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4609</v>
+        <v>-1.6325</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4031</v>
+        <v>-1.0375</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0578</v>
+        <v>-0.595</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.179</v>
+        <v>-0.5327</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2125</v>
+        <v>0.461</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0335</v>
+        <v>-0.9937</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1616</v>
+        <v>0.1104</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6113</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7729</v>
+        <v>0.1104</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3405</v>
+        <v>-0.6431</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6012</v>
+        <v>0.461</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.1041</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6237</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5246</v>
+        <v>-0.4039</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6542</v>
+        <v>0.0119</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1296</v>
+        <v>-0.4158</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1829</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.8994</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. SHAHRVIN</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.902</v>
+        <v>-2.5829</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2734</v>
+        <v>-1.6258</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6286</v>
+        <v>-0.957</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5327</v>
+        <v>-1.179</v>
       </c>
       <c r="H10" t="n">
-        <v>0.461</v>
+        <v>-1.2125</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9937</v>
+        <v>0.0335</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1104</v>
+        <v>0.1616</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.6113</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1104</v>
+        <v>0.7729</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6431</v>
+        <v>-1.3405</v>
       </c>
       <c r="N10" t="n">
-        <v>0.461</v>
+        <v>-0.6012</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1041</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6734</v>
+        <v>1.4027</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.224</v>
+        <v>1.4314</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4494</v>
+        <v>-0.0288</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.1829</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.8994</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9145</v>
+        <v>-3.0257</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0286</v>
+        <v>0.7494</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.9431</v>
+        <v>-3.7751</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4657</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6234</v>
+        <v>0.5122</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9831</v>
+        <v>0.704</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3598</v>
+        <v>-0.1918</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5864</v>
+        <v>-3.3169</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5828</v>
+        <v>-1.3469</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0036</v>
+        <v>-1.97</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3127</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9722</v>
+        <v>-0.7027</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1098</v>
+        <v>0.1261</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8623</v>
+        <v>-0.8287</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2933</v>
+        <v>-4.3769</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2592</v>
+        <v>-3.1412</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0341</v>
+        <v>-1.2357</v>
       </c>
       <c r="G13" t="n">
         <v>-4.3957</v>
@@ -1468,13 +1468,13 @@
         <v>0.4639</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7108</v>
+        <v>0.6271</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3541</v>
+        <v>0.472</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3567</v>
+        <v>0.1551</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.2942</v>
+        <v>-7.9206</v>
       </c>
       <c r="E14" t="n">
-        <v>7.457299999999998</v>
+        <v>7.8309</v>
       </c>
       <c r="F14" t="n">
         <v>-15.7514</v>
@@ -1513,16 +1513,16 @@
         <v>-11.5834</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.827800000000001</v>
+        <v>-5.8278</v>
       </c>
       <c r="I14" t="n">
         <v>-5.755599999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>6.288699999999999</v>
+        <v>6.2887</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1838000000000004</v>
+        <v>0.1837999999999995</v>
       </c>
       <c r="L14" t="n">
         <v>6.1048</v>
@@ -1531,7 +1531,7 @@
         <v>-17.8721</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.0117</v>
+        <v>-6.011699999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-11.8605</v>
@@ -1546,13 +1546,13 @@
         <v>11.5979</v>
       </c>
       <c r="S14" t="n">
-        <v>1.317899999999999</v>
+        <v>1.6912</v>
       </c>
       <c r="T14" t="n">
-        <v>6.0183</v>
+        <v>6.3919</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.7005</v>
+        <v>-4.700399999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.9715</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.479</v>
+        <v>7.98</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6752</v>
+        <v>6.2649</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8038</v>
+        <v>1.7151</v>
       </c>
       <c r="G15" t="n">
         <v>4.9736</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2653</v>
+        <v>0.2357</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2082</v>
+        <v>0.3815</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0571</v>
+        <v>-0.1458</v>
       </c>
       <c r="V15" t="n">
         <v>2.5387</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.224</v>
+        <v>5.6108</v>
       </c>
       <c r="E16" t="n">
-        <v>4.2695</v>
+        <v>4.8592</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0455</v>
+        <v>0.7516</v>
       </c>
       <c r="G16" t="n">
         <v>6.2077</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1461</v>
+        <v>0.2407</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.094</v>
+        <v>0.4957</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0521</v>
+        <v>-0.255</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5816</v>
+        <v>3.6932</v>
       </c>
       <c r="E17" t="n">
-        <v>4.5167</v>
+        <v>4.0449</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9351</v>
+        <v>-0.3517</v>
       </c>
       <c r="G17" t="n">
         <v>3.3068</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1195</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1404</v>
+        <v>0.6686</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2599</v>
+        <v>-0.6765</v>
       </c>
       <c r="V17" t="n">
         <v>0.3943</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4917</v>
+        <v>1.817</v>
       </c>
       <c r="E18" t="n">
         <v>0.4655</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0262</v>
+        <v>1.3515</v>
       </c>
       <c r="G18" t="n">
         <v>1.3796</v>
@@ -1858,13 +1858,13 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3519</v>
+        <v>-0.0266</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2025</v>
+        <v>0.1228</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7739</v>
+        <v>1.4837</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6823</v>
+        <v>2.1152</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0916</v>
+        <v>-0.6315</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7951</v>
+        <v>1.7139</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1719</v>
+        <v>1.7439</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.967</v>
+        <v>-0.03</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1518</v>
+        <v>1.8602</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4908</v>
+        <v>1.3584</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6425999999999999</v>
+        <v>0.5018</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6433</v>
+        <v>-0.1463</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.319</v>
+        <v>0.3856</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3243</v>
+        <v>-0.5319</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1964</v>
+        <v>-0.0679</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6923</v>
+        <v>0.2008</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8887</v>
+        <v>-0.2686</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1418</v>
+        <v>-0.3943</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>1.214</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.675</v>
+        <v>1.3148</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2271</v>
+        <v>3.6989</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5521</v>
+        <v>-2.3841</v>
       </c>
       <c r="G20" t="n">
         <v>1.4011</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5996</v>
+        <v>0.0402</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1142</v>
+        <v>0.586</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7139</v>
+        <v>-0.5458</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7501</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2033</v>
+        <v>1.1285</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4075</v>
+        <v>0.8003</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2041</v>
+        <v>0.3282</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7139</v>
+        <v>-0.7951</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7439</v>
+        <v>0.1719</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.03</v>
+        <v>-0.967</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8602</v>
+        <v>-0.1518</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3584</v>
+        <v>0.4908</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5018</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1463</v>
+        <v>-0.6433</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3856</v>
+        <v>-0.319</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5319</v>
+        <v>-0.3243</v>
       </c>
       <c r="P21" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3482</v>
+        <v>0.1582</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.507</v>
+        <v>0.8103</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8413</v>
+        <v>-0.6521</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="W21" t="n">
-        <v>1.214</v>
+        <v>0.1418</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. ROGKAVOPOULOS</t>
+          <t>P. KALAITZAKIS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7428</v>
+        <v>-0.6792</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8274</v>
+        <v>-0.6684</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0108</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9959</v>
+        <v>-0.7971</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.156</v>
+        <v>-0.168</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8399</v>
+        <v>-0.6291</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7527</v>
+        <v>-0.7863</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0336</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>-0.7863</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2431</v>
+        <v>-0.0108</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1896</v>
+        <v>-0.168</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0535</v>
+        <v>0.1573</v>
       </c>
       <c r="P22" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0211</v>
+        <v>0.118</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0747</v>
+        <v>0.118</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0958</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. KALAITZAKIS</t>
+          <t>N. ROGKAVOPOULOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7971</v>
+        <v>-0.8937</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7863</v>
+        <v>-0.7095</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0108</v>
+        <v>-0.1843</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7971</v>
+        <v>-0.9959</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.168</v>
+        <v>-0.156</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6291</v>
+        <v>-0.8399</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7863</v>
+        <v>-0.7527</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.0336</v>
       </c>
       <c r="L23" t="n">
         <v>-0.7863</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0108</v>
+        <v>-0.2431</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.168</v>
+        <v>-0.1896</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1573</v>
+        <v>-0.0535</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-0.1298</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>0.0433</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>-0.1731</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8349</v>
+        <v>-3.5028</v>
       </c>
       <c r="E24" t="n">
-        <v>3.3365</v>
+        <v>0.3877</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.1714</v>
+        <v>-3.8904</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6051</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>4.0587</v>
+        <v>1.3908</v>
       </c>
       <c r="T24" t="n">
-        <v>4.5336</v>
+        <v>1.5848</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4749</v>
+        <v>-0.1939</v>
       </c>
       <c r="V24" t="n">
         <v>0.031</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.7596</v>
+        <v>-6.5128</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.4264</v>
+        <v>-4.7187</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3332</v>
+        <v>-1.7942</v>
       </c>
       <c r="G25" t="n">
         <v>-2.206</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3706</v>
+        <v>-0.1239</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7468</v>
+        <v>-0.0391</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6238</v>
+        <v>-0.0848</v>
       </c>
       <c r="V25" t="n">
         <v>-2.7912</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.2941</v>
+        <v>11.4395</v>
       </c>
       <c r="E26" t="n">
-        <v>16.5402</v>
+        <v>16.54</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.246</v>
+        <v>-5.1006</v>
       </c>
       <c r="G26" t="n">
         <v>11.5835</v>
       </c>
       <c r="H26" t="n">
-        <v>5.827999999999999</v>
+        <v>5.828</v>
       </c>
       <c r="I26" t="n">
         <v>5.755500000000001</v>
@@ -2458,7 +2458,7 @@
         <v>17.8724</v>
       </c>
       <c r="K26" t="n">
-        <v>6.0118</v>
+        <v>6.011799999999999</v>
       </c>
       <c r="L26" t="n">
         <v>11.8605</v>
@@ -2473,7 +2473,7 @@
         <v>-6.1047</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0001999999999997559</v>
+        <v>0.0002000000000002</v>
       </c>
       <c r="Q26" t="n">
         <v>-11.5977</v>
@@ -2482,13 +2482,13 @@
         <v>11.5978</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.317800000000001</v>
+        <v>1.8275</v>
       </c>
       <c r="T26" t="n">
-        <v>4.700399999999999</v>
+        <v>4.700499999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.018400000000001</v>
+        <v>-2.8728</v>
       </c>
       <c r="V26" t="n">
         <v>-1.9716</v>
